--- a/06-content-engine/checkpoints/content-workbook-demo.xlsx
+++ b/06-content-engine/checkpoints/content-workbook-demo.xlsx
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -749,6 +749,7 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -787,6 +788,11 @@
           <t>Ghi chú</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ảnh Drive</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -824,6 +830,11 @@
           <t>2 chỗ [cần bổ sung]: học phí, ngày khai giảng</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/uc?export=view&amp;id=DEMO_FILE_ID</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -857,6 +868,7 @@
           <t>Duyệt cột Hình ảnh trước khi chuyển sang B7</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1107,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1117,6 +1129,7 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,6 +1168,11 @@
           <t>Ghi chú</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ảnh Drive</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1190,6 +1208,11 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Duyệt trong lớp. DỪNG ở Approved — không đăng thật.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/uc?export=view&amp;id=DEMO_FILE_ID</t>
         </is>
       </c>
     </row>

--- a/06-content-engine/checkpoints/content-workbook-demo.xlsx
+++ b/06-content-engine/checkpoints/content-workbook-demo.xlsx
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -749,7 +749,6 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -788,11 +787,6 @@
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Ảnh Drive</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -830,11 +824,6 @@
           <t>2 chỗ [cần bổ sung]: học phí, ngày khai giảng</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/uc?export=view&amp;id=DEMO_FILE_ID</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -868,7 +857,6 @@
           <t>Duyệt cột Hình ảnh trước khi chuyển sang B7</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1119,7 +1107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1129,7 +1117,6 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1168,11 +1155,6 @@
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Ảnh Drive</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1208,11 +1190,6 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Duyệt trong lớp. DỪNG ở Approved — không đăng thật.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/uc?export=view&amp;id=DEMO_FILE_ID</t>
         </is>
       </c>
     </row>
